--- a/Luban/Config/Datas/Levels/L27/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L27/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L27 W1/25; N=57; EHP=378.708000; normal:17x28,normal:18x29</t>
+          <t>L27 W1/25; N=57; EHP=1042.371404; normal:17x28,normal:18x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L27 W2/25; N=63; EHP=438.286741; normal:17x32,normal:18x31</t>
+          <t>L27 W2/25; N=63; EHP=1206.358370; normal:17x32,normal:18x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10020792,10020794,10049036,10020792,10020794,10049036,10020792,10020794,10049037,10020792,10020794,10049038,10020792,10020794,10049038,10020792,10020794,10049039,10020792,10020794,10049039,10020792,10020794,10049040,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020792,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793</t>
+          <t>10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020794,10020792,10020792,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020793,10020792,10020792,10020792,10020792,10020792,10020792,10020792,10020792</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L27 W3/25; N=69; EHP=531.052262; air:2x2,air:11x1,air:12x2,air:13x2,air:14x1,normal:17x21,normal:18x21,swarm:84x19</t>
+          <t>L27 W3/25; N=69; EHP=1572.672490; normal:17x29,normal:18x21,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>10020795,10020797,10049041,10020795,10020797,10049041,10020795,10020797,10049042,10020795,10020797,10049042,10020795,10020797,10049043,10020795,10020797,10049044,10020795,10020797,10049044,10020795,10020797,10049045,10020795,10020797,10049045,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020795,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796</t>
+          <t>10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020797,10020795,10020795,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020796,10020795,10020795,10020795,10020795,10020795,10020795,10020795,10020795,10020795</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L27 W4/25; N=75; EHP=666.000000; air:2x2,air:11x2,air:12x1,air:13x2,air:14x2,normal:17x23,normal:18x22,swarm:84x21</t>
+          <t>L27 W4/25; N=75; EHP=1977.846114; normal:17x32,normal:18x22,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>10020798,10020801,10049046,10020800,10020798,10020801,10049046,10020800,10020798,10020801,10049047,10020800,10020798,10020801,10049047,10020800,10020798,10020801,10049048,10020802,10020798,10020801,10049048,10020802,10020798,10020801,10049049,10020802,10020798,10020801,10049049,10020802,10020798,10020801,10049050,10020803,10020798,10020801,10049050,10020803,10020798,10020801,10020803,10020798,10020801,10020803,10020798,10020801,10020798,10020801,10020798,10020801,10020798,10020801,10020798,10020801,10020798,10020801,10020799,10020801,10020799,10020801,10020799,10020801,10020799,10020801,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799</t>
+          <t>10020798,10049046,10049046,10020800,10020798,10049046,10049046,10020800,10020798,10049047,10049047,10020800,10020798,10049047,10049047,10020800,10020798,10049048,10049048,10020802,10020798,10049048,10049048,10020802,10020798,10049049,10049049,10020802,10020798,10049049,10049049,10020802,10020798,10049050,10049050,10020803,10020798,10049050,10049050,10020803,10020798,10020801,10020803,10020798,10020801,10020803,10020798,10020801,10020798,10020801,10020798,10020801,10020798,10020801,10020798,10020801,10020798,10020801,10020799,10020801,10020799,10020801,10020799,10020801,10020799,10020801,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799,10020799</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L27 W5/25; N=81; EHP=1241.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x18,normal:18x19,medium:83x4,swarm:84x22,medium:108x4,medium:123x4</t>
+          <t>L27 W5/25; N=81; EHP=3460.605707; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x4,medium:123x4,normal:17x18,normal:18x19,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>10020807,10020813,10020809,10049051,10020812,10020807,10020813,10020809,10049051,10020812,10020807,10020813,10020810,10020804,10020812,10020807,10020813,10020810,10020804,10020812,10020807,10020813,10020810,10049052,10020812,10020807,10020813,10020811,10049052,10020815,10020807,10020813,10020811,10020805,10020815,10020807,10020813,10020814,10020805,10020815,10020807,10020813,10020814,10020806,10020815,10020807,10020813,10020814,10020806,10020816,10020807,10020813,10020816,10020807,10020813,10020816,10020807,10020813,10020816,10020807,10020813,10020807,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020808,10020808,10020808,10020808,10020808</t>
+          <t>10020807,10049051,10020809,10049051,10020812,10020807,10049051,10020809,10049051,10020812,10020807,10020804,10020810,10020804,10020812,10020807,10020804,10020810,10020804,10020812,10020807,10049052,10020810,10049052,10020812,10020807,10049052,10020811,10049052,10020815,10020807,10020805,10020811,10020805,10020815,10020807,10020805,10020814,10020805,10020815,10020807,10020806,10020814,10020806,10020815,10020807,10020806,10020814,10020806,10020816,10020807,10020813,10020816,10020807,10020813,10020816,10020807,10020813,10020816,10020807,10020813,10020807,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020813,10020808,10020808,10020808,10020808,10020808,10020808</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L27 W6/25; N=87; EHP=1266.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x2,fast:58x3,fast:64x2,medium:83x5,swarm:84x24,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L27 W6/25; N=87; EHP=3527.769788; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x3,medium:83x5,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>10020820,10020826,10020822,10049053,10020825,10020820,10020826,10020822,10049053,10020825,10020820,10020826,10020822,10020817,10020825,10020820,10020826,10020823,10020817,10020825,10020820,10020826,10020823,10049054,10020828,10020820,10020826,10020823,10049054,10020828,10020820,10020826,10020824,10020818,10020828,10020820,10020826,10020824,10020818,10020828,10020820,10020826,10020824,10020819,10020829,10020820,10020826,10020827,10020819,10020829,10020820,10020826,10020827,10020819,10020829,10020820,10020826,10020829,10020820,10020826,10020829,10020820,10020826,10020820,10020826,10020820,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020821,10020821,10020821,10020821,10020821</t>
+          <t>10020820,10049053,10020822,10049053,10020825,10020820,10049053,10020822,10049053,10020825,10020820,10020817,10020822,10020817,10020825,10020820,10020817,10020823,10020817,10020825,10020820,10049054,10020823,10049054,10020828,10020820,10049054,10020823,10049054,10020828,10020820,10020818,10020824,10020818,10020828,10020820,10020818,10020824,10020818,10020828,10020820,10020819,10020824,10020819,10020829,10020820,10020819,10020827,10020819,10020829,10020820,10020819,10020827,10020819,10020829,10020820,10020826,10020829,10020820,10020826,10020829,10020820,10020826,10020820,10020826,10020820,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020826,10020821,10020821,10020821,10020821,10020821,10020821</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L27 W7/25; N=93; EHP=1420.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x3,normal:17x16,normal:18x16,fast:30x3,fast:58x3,fast:64x3,medium:83x4,swarm:84x26,fast:98x2,medium:108x4,medium:123x5</t>
+          <t>L27 W7/25; N=93; EHP=3958.868396; air:2x4,air:11x4,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x5,normal:17x16,normal:18x16,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>10020833,10020839,10020835,10049055,10020838,10020833,10020839,10020835,10049055,10020838,10020833,10020839,10020835,10049055,10020838,10020833,10020839,10020836,10020830,10020838,10020833,10020839,10020836,10020830,10020838,10020833,10020839,10020837,10049056,10020841,10020833,10020839,10020837,10049056,10020841,10020833,10020839,10020837,10049056,10020841,10020833,10020839,10020840,10020831,10020841,10020833,10020839,10020840,10020831,10020841,10020833,10020839,10020840,10020832,10020842,10020833,10020839,10020832,10020842,10020833,10020839,10020842,10020833,10020839,10020842,10020833,10020839,10020833,10020839,10020833,10020839,10020833,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020834,10020834,10020834,10020834,10020834,10020834,10020834</t>
+          <t>10020833,10049055,10020835,10049055,10020838,10020833,10049055,10020835,10049055,10020838,10020833,10049055,10020835,10049055,10020838,10020833,10020830,10020836,10020830,10020838,10020833,10020830,10020836,10020830,10020838,10020833,10049056,10020837,10049056,10020841,10020833,10049056,10020837,10049056,10020841,10020833,10049056,10020837,10049056,10020841,10020833,10020831,10020840,10020831,10020841,10020833,10020831,10020840,10020831,10020841,10020833,10020832,10020840,10020832,10020842,10020833,10020832,10020832,10020842,10020833,10020839,10020842,10020833,10020839,10020842,10020833,10020839,10020833,10020839,10020833,10020839,10020833,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020839,10020834,10020834,10020834,10020834,10020834,10020834,10020834,10020834</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L27 W8/25; N=99; EHP=1824.000000; air:2x3,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x18,normal:18x17,fast:30x3,fast:58x2,fast:64x3,medium:83x5,swarm:84x27,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L27 W8/25; N=99; EHP=5086.583371; air:2x6,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x4,normal:17x18,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>10020846,10020852,10020848,10049057,10020851,10020846,10020852,10020848,10049057,10020851,10020846,10020852,10020848,10049057,10020851,10020846,10020852,10020849,10020843,10020851,10020846,10020852,10020849,10020843,10020851,10020846,10020852,10020849,10020843,10020854,10020846,10020852,10020850,10049058,10020854,10020846,10020852,10020850,10049058,10020854,10020846,10020852,10020850,10020844,10020854,10020846,10020852,10020853,10020844,10020854,10020846,10020852,10020853,10020844,10020855,10020846,10020852,10020853,10020845,10020855,10020846,10020852,10020845,10020855,10020846,10020852,10020855,10020846,10020852,10020855,10020846,10020852,10020846,10020852,10020846,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020847,10020847,10020847,10020847,10020847,10020847</t>
+          <t>10020846,10049057,10020848,10049057,10020851,10020846,10049057,10020848,10049057,10020851,10020846,10049057,10020848,10049057,10020851,10020846,10020843,10020849,10020843,10020851,10020846,10020843,10020849,10020843,10020851,10020846,10020843,10020849,10020843,10020854,10020846,10049058,10020850,10049058,10020854,10020846,10049058,10020850,10049058,10020854,10020846,10020844,10020850,10020844,10020854,10020846,10020844,10020853,10020844,10020854,10020846,10020844,10020853,10020844,10020855,10020846,10020845,10020853,10020845,10020855,10020846,10020845,10020845,10020855,10020846,10020852,10020855,10020846,10020852,10020855,10020846,10020852,10020846,10020852,10020846,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020852,10020847,10020847,10020847,10020847,10020847,10020847,10020847</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L27 W9/25; N=105; EHP=2326.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L27 W9/25; N=105; EHP=6488.514049; air:2x6,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>10020859,10020865,10020861,10049059,10020864,10020859,10020865,10020861,10049059,10020864,10020859,10020865,10020861,10020856,10020864,10020859,10020865,10020862,10020856,10020864,10020859,10020865,10020862,10020856,10020864,10020859,10020865,10020862,10049060,10020867,10020859,10020865,10020863,10049060,10020867,10020859,10020865,10020863,10020857,10020867,10020859,10020865,10020863,10020857,10020867,10020859,10020865,10020866,10020857,10020867,10020859,10020865,10020866,10020858,10020868,10020859,10020865,10020866,10020858,10020868,10020859,10020865,10020866,10020858,10020868,10020859,10020865,10020868,10020859,10020865,10020868,10020859,10020865,10020868,10020859,10020865,10020859,10020865,10020859,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020860,10020860,10020860,10020860,10020860,10020860</t>
+          <t>10020859,10049059,10020861,10049059,10020864,10020859,10049059,10020861,10049059,10020864,10020859,10020856,10020861,10020856,10020864,10020859,10020856,10020862,10020856,10020864,10020859,10020856,10020862,10020856,10020864,10020859,10049060,10020862,10049060,10020867,10020859,10049060,10020863,10049060,10020867,10020859,10020857,10020863,10020857,10020867,10020859,10020857,10020863,10020857,10020867,10020859,10020857,10020866,10020857,10020867,10020859,10020858,10020866,10020858,10020868,10020859,10020858,10020866,10020858,10020868,10020859,10020858,10020866,10020858,10020868,10020859,10020865,10020868,10020859,10020865,10020868,10020859,10020865,10020868,10020859,10020865,10020859,10020865,10020859,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020865,10020860,10020860,10020860,10020860,10020860,10020860,10020860</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L27 W10/25; N=111; EHP=4287.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x19,normal:18x19,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x31,fast:98x4,medium:108x5,medium:123x6</t>
+          <t>L27 W10/25; N=111; EHP=11949.735132; air:2x4,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x3,fast:98x4,medium:83x5,medium:108x5,medium:123x6,normal:17x19,normal:18x19,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>10020869,10020879,10020871,10049061,10020878,10020872,10020869,10020879,10020871,10049061,10020878,10045296,10020869,10020879,10020871,10049061,10020878,10020875,10020869,10020879,10020873,10049062,10020878,10020875,10020869,10020879,10020873,10049062,10020878,10020876,10020869,10020879,10020873,10049062,10020878,10020876,10020869,10020879,10020873,10049063,10020883,10020877,10020869,10020879,10020874,10049063,10020883,10020880,10020869,10020879,10020874,10049063,10020883,10020881,10020869,10020879,10020874,10049064,10020883,10020881,10020869,10020879,10020874,10049064,10020883,10045297,10020869,10020879,10020882,10049065,10020883,10020869,10020879,10020882,10049065,10020884,10020869,10020879,10020882,10049065,10020884,10020870,10020879,10020884,10020870,10020879,10020884,10020870,10020879,10020884,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020879,10020879,10020879</t>
+          <t>10020869,10049061,10020871,10049061,10020878,10020872,10020869,10049061,10020871,10049061,10020878,10045296,10020869,10049061,10020871,10049061,10020878,10020875,10020869,10049062,10020873,10049062,10020878,10020875,10020869,10049062,10020873,10049062,10020878,10020876,10020869,10049062,10020873,10049062,10020878,10020876,10020869,10049063,10020873,10049063,10020883,10020877,10020869,10049063,10020874,10049063,10020883,10020880,10020869,10049063,10020874,10049063,10020883,10020881,10020869,10049064,10020874,10049064,10020883,10020881,10020869,10049064,10020874,10049064,10020883,10045297,10020869,10049065,10020882,10049065,10020883,10020869,10049065,10020882,10049065,10020884,10020869,10049065,10020882,10049065,10020884,10020870,10020879,10020884,10020870,10020879,10020884,10020870,10020879,10020884,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020870,10020879,10020879,10020879,10020879</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L27 W11/25; N=117; EHP=4373.000000; air:2x3,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x15,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x32,heavy:86x1,heavy:88x2,fast:98x3,medium:108x6,medium:123x5,heavy:127x1</t>
+          <t>L27 W11/25; N=117; EHP=12175.573649; air:2x6,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x5,normal:17x14,normal:18x15,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>10020888,10020898,10020890,10049066,10020897,10020891,10020888,10020898,10020890,10049066,10020897,10020892,10020888,10020898,10020890,10049066,10020897,10020895,10020888,10020898,10020890,10020885,10020897,10020895,10020888,10020898,10020893,10020885,10020897,10045298,10020888,10020898,10020893,10020885,10020897,10020896,10020888,10020898,10020893,10049067,10020902,10020896,10020888,10020898,10020894,10049067,10020902,10020899,10020888,10020898,10020894,10049067,10020902,10020899,10020888,10020898,10020894,10020886,10020902,10020900,10020888,10020898,10020894,10020886,10020902,10020900,10020888,10020898,10020901,10020886,10020902,10045299,10020888,10020898,10020901,10020887,10020903,10020888,10020898,10020901,10020887,10020903,10020888,10020898,10020887,10020903,10020889,10020898,10020903,10020889,10020898,10020903,10020889,10020898,10020903,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020898,10020898,10020898,10020898</t>
+          <t>10020888,10049066,10020890,10049066,10020897,10020891,10020888,10049066,10020890,10049066,10020897,10020892,10020888,10049066,10020890,10049066,10020897,10020895,10020888,10020885,10020890,10020885,10020897,10020895,10020888,10020885,10020893,10020885,10020897,10045298,10020888,10020885,10020893,10020885,10020897,10020896,10020888,10049067,10020893,10049067,10020902,10020896,10020888,10049067,10020894,10049067,10020902,10020899,10020888,10049067,10020894,10049067,10020902,10020899,10020888,10020886,10020894,10020886,10020902,10020900,10020888,10020886,10020894,10020886,10020902,10020900,10020888,10020886,10020901,10020886,10020902,10045299,10020888,10020887,10020901,10020887,10020903,10020888,10020887,10020901,10020887,10020903,10020888,10020887,10020887,10020903,10020889,10020898,10020903,10020889,10020898,10020903,10020889,10020898,10020903,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020889,10020898,10020898,10020898,10020898,10020898</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L27 W12/25; N=123; EHP=4524.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x15,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x2,heavy:88x2,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L27 W12/25; N=123; EHP=12598.250757; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x15,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>10020907,10020916,10020909,10049068,10020915,10020910,10020907,10020916,10020909,10049068,10020915,10020910,10020907,10020916,10020909,10049068,10020915,10020911,10020907,10020916,10020909,10020904,10020915,10045300,10020907,10020916,10020912,10020904,10020915,10045301,10020907,10020916,10020912,10020904,10020915,10020914,10020907,10020916,10020912,10049069,10020920,10020914,10020907,10020916,10020912,10049069,10020920,10020917,10020907,10020916,10020913,10049069,10020920,10020917,10020907,10020916,10020913,10020905,10020920,10020918,10020907,10020916,10020913,10020905,10020920,10020918,10020907,10020916,10020919,10020905,10020920,10020922,10020907,10020916,10020919,10020906,10020921,10020907,10020916,10020919,10020906,10020921,10020907,10020916,10020919,10020906,10020921,10020907,10020916,10020921,10020908,10020916,10020921,10020908,10020916,10020921,10020908,10020916,10020921,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020916,10020916,10020916,10020916</t>
+          <t>10020907,10049068,10020909,10049068,10020915,10020910,10020907,10049068,10020909,10049068,10020915,10020910,10020907,10049068,10020909,10049068,10020915,10020911,10020907,10020904,10020909,10020904,10020915,10045300,10020907,10020904,10020912,10020904,10020915,10045301,10020907,10020904,10020912,10020904,10020915,10020914,10020907,10049069,10020912,10049069,10020920,10020914,10020907,10049069,10020912,10049069,10020920,10020917,10020907,10049069,10020913,10049069,10020920,10020917,10020907,10020905,10020913,10020905,10020920,10020918,10020907,10020905,10020913,10020905,10020920,10020918,10020907,10020905,10020919,10020905,10020920,10020922,10020907,10020906,10020919,10020906,10020921,10020907,10020906,10020919,10020906,10020921,10020907,10020906,10020919,10020906,10020921,10020907,10020916,10020921,10020908,10020916,10020921,10020908,10020916,10020921,10020908,10020916,10020921,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020908,10020916,10020916,10020916,10020916,10020916</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L27 W13/25; N=129; EHP=5518.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x1,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x36,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x7,heavy:127x1</t>
+          <t>L27 W13/25; N=129; EHP=15358.492718; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>10020926,10020937,10020928,10049070,10020936,10020929,10020926,10020937,10020928,10049070,10020936,10020929,10020926,10020937,10020928,10049070,10020936,10020930,10020926,10020937,10020928,10049070,10020936,10020930,10020926,10020937,10020931,10020923,10020936,10020933,10020926,10020937,10020931,10020923,10020936,10020934,10020926,10020937,10020931,10020923,10020936,10020935,10020926,10020937,10020931,10049071,10020940,10020935,10020926,10020937,10020932,10049071,10020940,10020938,10020926,10020937,10020932,10049071,10020940,10020938,10020926,10020937,10020932,10020924,10020940,10045302,10020926,10020937,10020932,10020924,10020940,10020942,10020926,10020937,10020939,10020924,10020940,10020942,10020926,10020937,10020939,10020925,10020940,10020926,10020937,10020939,10020925,10020941,10020926,10020937,10020939,10020925,10020941,10020926,10020937,10020941,10020927,10020937,10020941,10020927,10020937,10020941,10020927,10020937,10020941,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020937,10020937,10020937,10020937</t>
+          <t>10020926,10049070,10020928,10049070,10020936,10020929,10020926,10049070,10020928,10049070,10020936,10020929,10020926,10049070,10020928,10049070,10020936,10020930,10020926,10049070,10020928,10049070,10020936,10020930,10020926,10020923,10020931,10020923,10020936,10020933,10020926,10020923,10020931,10020923,10020936,10020934,10020926,10020923,10020931,10020923,10020936,10020935,10020926,10049071,10020931,10049071,10020940,10020935,10020926,10049071,10020932,10049071,10020940,10020938,10020926,10049071,10020932,10049071,10020940,10020938,10020926,10020924,10020932,10020924,10020940,10045302,10020926,10020924,10020932,10020924,10020940,10020942,10020926,10020924,10020939,10020924,10020940,10020942,10020926,10020925,10020939,10020925,10020940,10020926,10020925,10020939,10020925,10020941,10020926,10020925,10020939,10020925,10020941,10020926,10020937,10020941,10020927,10020937,10020941,10020927,10020937,10020941,10020927,10020937,10020941,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020927,10020937,10020937,10020937,10020937,10020937</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L27 W14/25; N=135; EHP=6655.000000; air:2x4,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x17,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x37,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L27 W14/25; N=135; EHP=18526.166525; air:2x8,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x6,normal:17x17,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>10020946,10020957,10020948,10049072,10020956,10020949,10020953,10020946,10020957,10020948,10049072,10020956,10020949,10020946,10020957,10020948,10049072,10020956,10020950,10020946,10020957,10020948,10020943,10020956,10020950,10020946,10020957,10020951,10020943,10020956,10020954,10020946,10020957,10020951,10020943,10020956,10020954,10020946,10020957,10020951,10020943,10020956,10020955,10020946,10020957,10020951,10049073,10020961,10020955,10020946,10020957,10020952,10049073,10020961,10045303,10020946,10020957,10020952,10049073,10020961,10020958,10020946,10020957,10020952,10020944,10020961,10020958,10020946,10020957,10020952,10020944,10020961,10020959,10020946,10020957,10020960,10020944,10020961,10020963,10020946,10020957,10020960,10020944,10020961,10020963,10020946,10020957,10020960,10020945,10020962,10020946,10020957,10020960,10020945,10020962,10020947,10020957,10020945,10020962,10020947,10020957,10020962,10020947,10020957,10020962,10020947,10020957,10020962,10020947,10020957,10020962,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020957,10020957,10020957,10020957,10020957,10020957</t>
+          <t>10020946,10049072,10020948,10049072,10020956,10020949,10020953,10020946,10049072,10020948,10049072,10020956,10020949,10020946,10049072,10020948,10049072,10020956,10020950,10020946,10020943,10020948,10020943,10020956,10020950,10020946,10020943,10020951,10020943,10020956,10020954,10020946,10020943,10020951,10020943,10020956,10020954,10020946,10020943,10020951,10020943,10020956,10020955,10020946,10049073,10020951,10049073,10020961,10020955,10020946,10049073,10020952,10049073,10020961,10045303,10020946,10049073,10020952,10049073,10020961,10020958,10020946,10020944,10020952,10020944,10020961,10020958,10020946,10020944,10020952,10020944,10020961,10020959,10020946,10020944,10020960,10020944,10020961,10020963,10020946,10020944,10020960,10020944,10020961,10020963,10020946,10020945,10020960,10020945,10020962,10020946,10020945,10020960,10020945,10020962,10020947,10020945,10020945,10020962,10020947,10020957,10020962,10020947,10020957,10020962,10020947,10020957,10020962,10020947,10020957,10020962,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020947,10020957,10020957,10020957,10020957,10020957,10020957,10020957</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L27 W15/25; N=141; EHP=11614.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x39,heavy:86x2,heavy:88x1,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L27 W15/25; N=141; EHP=32326.979265; air:2x6,air:11x8,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>10020964,10020975,10020966,10049074,10020974,10020967,10020964,10020975,10020966,10049074,10020974,10020967,10020964,10020975,10020966,10049074,10020974,10020968,10020964,10020975,10020966,10049075,10020974,10020968,10020964,10020975,10020969,10049075,10020974,10020971,10020964,10020975,10020969,10049075,10020974,10020971,10020964,10020975,10020969,10049075,10020974,10020972,10020964,10020975,10020969,10049076,10020978,10020972,10020964,10020975,10020970,10049076,10020978,10020973,10020964,10020975,10020970,10049076,10020978,10045304,10020964,10020975,10020970,10049076,10020978,10020976,10020964,10020975,10020970,10049077,10020978,10020976,10020964,10020975,10020970,10049077,10020978,10020980,10020964,10020975,10020977,10049077,10020978,10020980,10020964,10020975,10020977,10049078,10020979,10020964,10020975,10020977,10049078,10020979,10020964,10020975,10020977,10049078,10020979,10020964,10020975,10049078,10020979,10020965,10020975,10020979,10020965,10020975,10020979,10020965,10020975,10020979,10020965,10020975,10020979,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020975,10020975,10020975,10020975,10020975,10020975</t>
+          <t>10020964,10049074,10020966,10049074,10020974,10020967,10020964,10049074,10020966,10049074,10020974,10020967,10020964,10049074,10020966,10049074,10020974,10020968,10020964,10049075,10020966,10049075,10020974,10020968,10020964,10049075,10020969,10049075,10020974,10020971,10020964,10049075,10020969,10049075,10020974,10020971,10020964,10049075,10020969,10049075,10020974,10020972,10020964,10049076,10020969,10049076,10020978,10020972,10020964,10049076,10020970,10049076,10020978,10020973,10020964,10049076,10020970,10049076,10020978,10045304,10020964,10049076,10020970,10049076,10020978,10020976,10020964,10049077,10020970,10049077,10020978,10020976,10020964,10049077,10020970,10049077,10020978,10020980,10020964,10049077,10020977,10049077,10020978,10020980,10020964,10049078,10020977,10049078,10020979,10020964,10049078,10020977,10049078,10020979,10020964,10049078,10020977,10049078,10020979,10020964,10049078,10049078,10020979,10020965,10020975,10020979,10020965,10020975,10020979,10020965,10020975,10020979,10020965,10020975,10020979,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020965,10020975,10020975,10020975,10020975,10020975,10020975,10020975</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L27 W16/25; N=147; EHP=11847.000000; air:2x3,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x41,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L27 W16/25; N=147; EHP=32993.303670; air:2x6,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x17,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>10020984,10020994,10020986,10049079,10020993,10045305,10020984,10020994,10020986,10049079,10020993,10020987,10020984,10020994,10020986,10049079,10020993,10020987,10020984,10020994,10020986,10049079,10020993,10020990,10020984,10020994,10020986,10020981,10020993,10020990,10020984,10020994,10020988,10020981,10020993,10020991,10020984,10020994,10020988,10020981,10020993,10020991,10020984,10020994,10020988,10049080,10020998,10020992,10020984,10020994,10020988,10049080,10020998,10020992,10020984,10020994,10020989,10049080,10020998,10020995,10020984,10020994,10020989,10049080,10020998,10020995,10020984,10020994,10020989,10020982,10020998,10020996,10020984,10020994,10020989,10020982,10020998,10020996,10020984,10020994,10020997,10020982,10020998,10021000,10020984,10020994,10020997,10020983,10020998,10021000,10020984,10020994,10020997,10020983,10020999,10020984,10020994,10020997,10020983,10020999,10020984,10020994,10020997,10020983,10020999,10020984,10020994,10020999,10020985,10020994,10020999,10020985,10020994,10020999,10020985,10020994,10020999,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020994,10020994,10020994,10020994</t>
+          <t>10020984,10049079,10020986,10049079,10020993,10045305,10020984,10049079,10020986,10049079,10020993,10020987,10020984,10049079,10020986,10049079,10020993,10020987,10020984,10049079,10020986,10049079,10020993,10020990,10020984,10020981,10020986,10020981,10020993,10020990,10020984,10020981,10020988,10020981,10020993,10020991,10020984,10020981,10020988,10020981,10020993,10020991,10020984,10049080,10020988,10049080,10020998,10020992,10020984,10049080,10020988,10049080,10020998,10020992,10020984,10049080,10020989,10049080,10020998,10020995,10020984,10049080,10020989,10049080,10020998,10020995,10020984,10020982,10020989,10020982,10020998,10020996,10020984,10020982,10020989,10020982,10020998,10020996,10020984,10020982,10020997,10020982,10020998,10021000,10020984,10020983,10020997,10020983,10020998,10021000,10020984,10020983,10020997,10020983,10020999,10020984,10020983,10020997,10020983,10020999,10020984,10020983,10020997,10020983,10020999,10020984,10020994,10020999,10020985,10020994,10020999,10020985,10020994,10020999,10020985,10020994,10020999,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020985,10020994,10020994,10020994,10020994,10020994</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L27 W17/25; N=153; EHP=12084.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x7,heavy:127x2</t>
+          <t>L27 W17/25; N=153; EHP=33636.793588; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x8,medium:123x7,normal:17x19,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>10021004,10021014,10021006,10049081,10021013,10021007,10021004,10021014,10021006,10049081,10021013,10021007,10021004,10021014,10021006,10049081,10021013,10045306,10021004,10021014,10021006,10049081,10021013,10021010,10021004,10021014,10021008,10021001,10021013,10021010,10021004,10021014,10021008,10021001,10021013,10021011,10021004,10021014,10021008,10021001,10021013,10021011,10021004,10021014,10021008,10021001,10021013,10021012,10021004,10021014,10021008,10049082,10021018,10021012,10021004,10021014,10021009,10049082,10021018,10021015,10021004,10021014,10021009,10049082,10021018,10021015,10021004,10021014,10021009,10049082,10021018,10021016,10021004,10021014,10021009,10021002,10021018,10021016,10021004,10021014,10021009,10021002,10021018,10021020,10021004,10021014,10021017,10021002,10021018,10021020,10021004,10021014,10021017,10021002,10021019,10021004,10021014,10021017,10021003,10021019,10021004,10021014,10021017,10021003,10021019,10021004,10021014,10021017,10021003,10021019,10021004,10021014,10021019,10021005,10021014,10021019,10021005,10021014,10021019,10021005,10021014,10021019,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021014,10021014,10021014,10021014,10021014</t>
+          <t>10021004,10049081,10021006,10049081,10021013,10021007,10021004,10049081,10021006,10049081,10021013,10021007,10021004,10049081,10021006,10049081,10021013,10045306,10021004,10049081,10021006,10049081,10021013,10021010,10021004,10021001,10021008,10021001,10021013,10021010,10021004,10021001,10021008,10021001,10021013,10021011,10021004,10021001,10021008,10021001,10021013,10021011,10021004,10021001,10021008,10021001,10021013,10021012,10021004,10049082,10021008,10049082,10021018,10021012,10021004,10049082,10021009,10049082,10021018,10021015,10021004,10049082,10021009,10049082,10021018,10021015,10021004,10049082,10021009,10049082,10021018,10021016,10021004,10021002,10021009,10021002,10021018,10021016,10021004,10021002,10021009,10021002,10021018,10021020,10021004,10021002,10021017,10021002,10021018,10021020,10021004,10021002,10021017,10021002,10021019,10021004,10021003,10021017,10021003,10021019,10021004,10021003,10021017,10021003,10021019,10021004,10021003,10021017,10021003,10021019,10021004,10021014,10021019,10021005,10021014,10021019,10021005,10021014,10021019,10021005,10021014,10021019,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021005,10021014,10021014,10021014,10021014,10021014,10021014</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L27 W18/25; N=159; EHP=12910.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x3,normal:17x20,normal:18x19,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L27 W18/25; N=159; EHP=35944.685444; air:2x8,air:11x8,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x20,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>10021024,10021035,10021026,10049083,10021034,10021027,10021024,10021035,10021026,10049083,10021034,10021027,10021024,10021035,10021026,10049083,10021034,10021028,10021024,10021035,10021026,10049083,10021034,10021028,10021024,10021035,10021026,10021021,10021034,10021031,10021024,10021035,10021029,10021021,10021034,10021031,10021024,10021035,10021029,10021021,10021034,10021032,10021024,10021035,10021029,10021021,10021034,10021032,10021024,10021035,10021029,10049084,10021039,10021033,10021024,10021035,10021029,10049084,10021039,10021033,10021024,10021035,10021030,10049084,10021039,10021036,10021024,10021035,10021030,10049084,10021039,10021036,10021024,10021035,10021030,10021022,10021039,10021037,10021024,10021035,10021030,10021022,10021039,10021037,10021024,10021035,10021030,10021022,10021039,10021041,10021024,10021035,10021038,10021022,10021039,10021041,10021024,10021035,10021038,10021023,10021040,10021024,10021035,10021038,10021023,10021040,10021024,10021035,10021038,10021023,10021040,10021024,10021035,10021023,10021040,10021025,10021035,10021040,10021025,10021035,10021040,10021025,10021035,10021040,10021025,10021035,10021040,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021035,10021035,10021035,10021035,10021035,10021035</t>
+          <t>10021024,10049083,10021026,10049083,10021034,10021027,10021024,10049083,10021026,10049083,10021034,10021027,10021024,10049083,10021026,10049083,10021034,10021028,10021024,10049083,10021026,10049083,10021034,10021028,10021024,10021021,10021026,10021021,10021034,10021031,10021024,10021021,10021029,10021021,10021034,10021031,10021024,10021021,10021029,10021021,10021034,10021032,10021024,10021021,10021029,10021021,10021034,10021032,10021024,10049084,10021029,10049084,10021039,10021033,10021024,10049084,10021029,10049084,10021039,10021033,10021024,10049084,10021030,10049084,10021039,10021036,10021024,10049084,10021030,10049084,10021039,10021036,10021024,10021022,10021030,10021022,10021039,10021037,10021024,10021022,10021030,10021022,10021039,10021037,10021024,10021022,10021030,10021022,10021039,10021041,10021024,10021022,10021038,10021022,10021039,10021041,10021024,10021023,10021038,10021023,10021040,10021024,10021023,10021038,10021023,10021040,10021024,10021023,10021038,10021023,10021040,10021024,10021023,10021023,10021040,10021025,10021035,10021040,10021025,10021035,10021040,10021025,10021035,10021040,10021025,10021035,10021040,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021025,10021035,10021035,10021035,10021035,10021035,10021035,10021035</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L27 W19/25; N=165; EHP=14953.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x46,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L27 W19/25; N=165; EHP=41638.480020; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>10021045,10021057,10021047,10049085,10021056,10021048,10021052,10021045,10021057,10021047,10049085,10021056,10021048,10021045,10021057,10021047,10049085,10021056,10021049,10021045,10021057,10021047,10049085,10021056,10021049,10021045,10021057,10021047,10021042,10021056,10021053,10021045,10021057,10021050,10021042,10021056,10021053,10021045,10021057,10021050,10021042,10021056,10021053,10021045,10021057,10021050,10021042,10021056,10021054,10021045,10021057,10021050,10049086,10021061,10021054,10021045,10021057,10021050,10049086,10021061,10021055,10021045,10021057,10021051,10049086,10021061,10021055,10021045,10021057,10021051,10049086,10021061,10021058,10021045,10021057,10021051,10021043,10021061,10021058,10021045,10021057,10021051,10021043,10021061,10021059,10021045,10021057,10021051,10021043,10021061,10021059,10021045,10021057,10021060,10021043,10021061,10021063,10021045,10021057,10021060,10021043,10021061,10021063,10021045,10021057,10021060,10021044,10021062,10021045,10021057,10021060,10021044,10021062,10021045,10021057,10021060,10021044,10021062,10021046,10021057,10021044,10021062,10021046,10021057,10021062,10021046,10021057,10021062,10021046,10021057,10021062,10021046,10021057,10021062,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021057,10021057,10021057,10021057,10021057,10021057,10021057</t>
+          <t>10021045,10049085,10021047,10049085,10021056,10021048,10021052,10021045,10049085,10021047,10049085,10021056,10021048,10021045,10049085,10021047,10049085,10021056,10021049,10021045,10049085,10021047,10049085,10021056,10021049,10021045,10021042,10021047,10021042,10021056,10021053,10021045,10021042,10021050,10021042,10021056,10021053,10021045,10021042,10021050,10021042,10021056,10021053,10021045,10021042,10021050,10021042,10021056,10021054,10021045,10049086,10021050,10049086,10021061,10021054,10021045,10049086,10021050,10049086,10021061,10021055,10021045,10049086,10021051,10049086,10021061,10021055,10021045,10049086,10021051,10049086,10021061,10021058,10021045,10021043,10021051,10021043,10021061,10021058,10021045,10021043,10021051,10021043,10021061,10021059,10021045,10021043,10021051,10021043,10021061,10021059,10021045,10021043,10021060,10021043,10021061,10021063,10021045,10021043,10021060,10021043,10021061,10021063,10021045,10021044,10021060,10021044,10021062,10021045,10021044,10021060,10021044,10021062,10021045,10021044,10021060,10021044,10021062,10021046,10021044,10021044,10021062,10021046,10021057,10021062,10021046,10021057,10021062,10021046,10021057,10021062,10021046,10021057,10021062,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021046,10021057,10021057,10021057,10021057,10021057,10021057,10021057,10021057</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L27 W20/25; N=171; EHP=25097.000000; air:2x4,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x20,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,elite:67x1,heavy:67x3,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L27 W20/25; N=171; EHP=69876.380258; air:2x8,air:11x8,air:12x8,air:13x10,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x20,normal:18x20,swarm:84x26 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10021067,10021078,10021069,10049087,10021077,10021070,10021067,10021078,10021069,10049087,10021077,10021070,10021067,10021078,10021069,10049087,10021077,10021071,10021067,10021078,10021069,10049087,10021077,10021071,10021067,10021078,10021069,10021064,10021077,10021074,10021067,10021078,10021069,10021064,10021077,10021074,10021067,10021078,10021072,10021064,10021077,10021075,10021067,10021078,10021072,10021064,10021077,10021075,10021067,10021078,10021072,10021064,10021077,10021076,10021067,10021078,10021072,10049088,10021082,10021076,10021067,10021078,10021072,10049088,10021082,10021079,10021067,10021078,10021073,10049088,10021082,10021079,10021067,10021078,10021073,10049088,10021082,10021080,10021067,10021078,10021073,10021065,10021082,10021080,10021067,10021078,10021073,10021065,10021082,10021080,10021067,10021078,10021073,10021065,10021082,10021084,10021067,10021078,10021081,10021065,10021082,10021084,10021067,10021078,10021081,10021066,10021083,10021067,10021078,10021081,10021066,10021083,10021067,10021078,10021081,10021066,10021083,10021067,10021078,10021081,10021066,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021078,10021078,10021078,10021078,10021078,10021078</t>
+          <t>10021067,10049087,10021069,10049087,10021077,10021070,10021067,10049087,10021069,10049087,10021077,10021070,10021067,10049087,10021069,10049087,10021077,10021071,10021067,10049087,10021069,10049087,10021077,10021071,10021067,10021064,10021069,10021064,10021077,10021074,10021067,10021064,10021069,10021064,10021077,10021074,10021067,10021064,10021072,10021064,10021077,10021075,10021067,10021064,10021072,10021064,10021077,10021075,10021067,10021064,10021072,10021064,10021077,10021076,10021067,10049088,10021072,10049088,10021082,10021076,10021067,10049088,10021072,10049088,10021082,10021079,10021067,10049088,10021073,10049088,10021082,10021079,10021067,10049088,10021073,10049088,10021082,10021080,10021067,10021065,10021073,10021065,10021082,10021080,10021067,10021065,10021073,10021065,10021082,10021080,10021067,10021065,10021073,10021065,10021082,10021084,10021067,10021065,10021081,10021065,10021082,10021084,10021067,10021066,10021081,10021066,10021083,10021067,10021066,10021081,10021066,10021083,10021067,10021066,10021081,10021066,10021083,10021067,10021066,10021081,10021066,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021083,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021068,10021078,10021078,10021078,10021078,10021078,10021078,10021078</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L27 W21/25; N=177; EHP=25599.000000; air:2x4,air:11x5,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x22,fast:30x6,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x3,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L27 W21/25; N=177; EHP=71264.989773; air:2x8,air:11x10,air:12x8,air:13x8,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x2,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10021088,10021099,10021090,10049089,10021098,10021091,10021088,10021099,10021090,10049089,10021098,10021091,10021088,10021099,10021090,10049089,10021098,10021092,10021088,10021099,10021090,10049089,10021098,10021092,10021088,10021099,10021090,10021085,10021098,10021095,10021088,10021099,10021093,10021085,10021098,10021095,10021088,10021099,10021093,10021085,10021098,10021096,10021088,10021099,10021093,10021085,10021098,10021096,10021088,10021099,10021093,10049090,10021098,10021097,10021088,10021099,10021093,10049090,10021103,10021097,10021088,10021099,10021094,10049090,10021103,10021097,10021088,10021099,10021094,10049090,10021103,10021100,10021088,10021099,10021094,10049090,10021103,10021100,10021088,10021099,10021094,10021086,10021103,10021100,10021088,10021099,10021094,10021086,10021103,10021101,10021088,10021099,10021102,10021086,10021103,10021101,10021088,10021099,10021102,10021086,10021103,10021105,10021088,10021099,10021102,10021087,10021103,10021105,10021088,10021099,10021102,10021087,10021104,10021088,10021099,10021102,10021087,10021104,10021088,10021099,10021102,10021087,10021104,10021088,10021099,10021087,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021099,10021099,10021099,10021099,10021099,10021099,10021099</t>
+          <t>10021088,10049089,10021090,10049089,10021098,10021091,10021088,10049089,10021090,10049089,10021098,10021091,10021088,10049089,10021090,10049089,10021098,10021092,10021088,10049089,10021090,10049089,10021098,10021092,10021088,10021085,10021090,10021085,10021098,10021095,10021088,10021085,10021093,10021085,10021098,10021095,10021088,10021085,10021093,10021085,10021098,10021096,10021088,10021085,10021093,10021085,10021098,10021096,10021088,10049090,10021093,10049090,10021098,10021097,10021088,10049090,10021093,10049090,10021103,10021097,10021088,10049090,10021094,10049090,10021103,10021097,10021088,10049090,10021094,10049090,10021103,10021100,10021088,10049090,10021094,10049090,10021103,10021100,10021088,10021086,10021094,10021086,10021103,10021100,10021088,10021086,10021094,10021086,10021103,10021101,10021088,10021086,10021102,10021086,10021103,10021101,10021088,10021086,10021102,10021086,10021103,10021105,10021088,10021087,10021102,10021087,10021103,10021105,10021088,10021087,10021102,10021087,10021104,10021088,10021087,10021102,10021087,10021104,10021088,10021087,10021102,10021087,10021104,10021088,10021087,10021087,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021104,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021089,10021099,10021099,10021099,10021099,10021099,10021099,10021099,10021099</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L27 W22/25; N=183; EHP=26111.000000; air:2x4,air:11x4,air:12x5,air:13x4,air:14x5,normal:17x22,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x51,heavy:86x3,heavy:88x2,fast:98x6,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L27 W22/25; N=183; EHP=72699.404362; air:2x8,air:11x8,air:12x10,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10021109,10021120,10021111,10049091,10021119,10021112,10021109,10021120,10021111,10049091,10021119,10021112,10021109,10021120,10021111,10049091,10021119,10021112,10021109,10021120,10021111,10049091,10021119,10021113,10021109,10021120,10021111,10049091,10021119,10021113,10021109,10021120,10021114,10021106,10021119,10021116,10021109,10021120,10021114,10021106,10021119,10021116,10021109,10021120,10021114,10021106,10021119,10021117,10021109,10021120,10021114,10021106,10021119,10021117,10021109,10021120,10021114,10049092,10021124,10021118,10021109,10021120,10021114,10049092,10021124,10021118,10021109,10021120,10021115,10049092,10021124,10021121,10021109,10021120,10021115,10049092,10021124,10021121,10021109,10021120,10021115,10049092,10021124,10021121,10021109,10021120,10021115,10021107,10021124,10021122,10021109,10021120,10021115,10021107,10021124,10021122,10021109,10021120,10021115,10021107,10021124,10021126,10021109,10021120,10021123,10021107,10021124,10021126,10021109,10021120,10021123,10021107,10021124,10021109,10021120,10021123,10021108,10021125,10021109,10021120,10021123,10021108,10021125,10021109,10021120,10021123,10021108,10021125,10021109,10021120,10021108,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021120,10021120,10021120,10021120,10021120,10021120</t>
+          <t>10021109,10049091,10021111,10049091,10021119,10021112,10021109,10049091,10021111,10049091,10021119,10021112,10021109,10049091,10021111,10049091,10021119,10021112,10021109,10049091,10021111,10049091,10021119,10021113,10021109,10049091,10021111,10049091,10021119,10021113,10021109,10021106,10021114,10021106,10021119,10021116,10021109,10021106,10021114,10021106,10021119,10021116,10021109,10021106,10021114,10021106,10021119,10021117,10021109,10021106,10021114,10021106,10021119,10021117,10021109,10049092,10021114,10049092,10021124,10021118,10021109,10049092,10021114,10049092,10021124,10021118,10021109,10049092,10021115,10049092,10021124,10021121,10021109,10049092,10021115,10049092,10021124,10021121,10021109,10049092,10021115,10049092,10021124,10021121,10021109,10021107,10021115,10021107,10021124,10021122,10021109,10021107,10021115,10021107,10021124,10021122,10021109,10021107,10021115,10021107,10021124,10021126,10021109,10021107,10021123,10021107,10021124,10021126,10021109,10021107,10021123,10021107,10021124,10021109,10021108,10021123,10021108,10021125,10021109,10021108,10021123,10021108,10021125,10021109,10021108,10021123,10021108,10021125,10021109,10021108,10021108,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021125,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021110,10021120,10021120,10021120,10021120,10021120,10021120,10021120</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L27 W23/25; N=189; EHP=26634.000000; air:2x5,air:11x4,air:12x5,air:13x5,air:14x4,normal:17x23,normal:18x23,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x3,heavy:88x2,fast:98x5,medium:108x10,medium:123x9,heavy:127x2</t>
+          <t>L27 W23/25; N=189; EHP=74168.545576; air:2x10,air:11x8,air:12x10,air:13x10,air:14x8,fast:30x5,fast:58x6,fast:64x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x10,medium:123x9,normal:17x23,normal:18x23,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10021130,10021141,10021132,10049093,10021140,10021133,10021130,10021141,10021132,10049093,10021140,10021133,10021130,10021141,10021132,10049093,10021140,10021133,10021130,10021141,10021132,10049093,10021140,10021134,10021130,10021141,10021132,10049093,10021140,10021134,10021130,10021141,10021132,10021127,10021140,10021134,10021130,10021141,10021135,10021127,10021140,10021137,10021130,10021141,10021135,10021127,10021140,10021137,10021130,10021141,10021135,10021127,10021140,10021138,10021130,10021141,10021135,10021127,10021140,10021138,10021130,10021141,10021135,10049094,10021145,10021139,10021130,10021141,10021136,10049094,10021145,10021139,10021130,10021141,10021136,10049094,10021145,10021142,10021130,10021141,10021136,10049094,10021145,10021142,10021130,10021141,10021136,10021128,10021145,10021143,10021130,10021141,10021136,10021128,10021145,10021143,10021130,10021141,10021136,10021128,10021145,10021147,10021130,10021141,10021144,10021128,10021145,10021147,10021130,10021141,10021144,10021128,10021145,10021147,10021130,10021141,10021144,10021129,10021146,10021130,10021141,10021144,10021129,10021146,10021130,10021141,10021144,10021129,10021146,10021130,10021141,10021144,10021129,10021146,10021130,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021141,10021141,10021141,10021141,10021141,10021141,10021141</t>
+          <t>10021130,10049093,10021132,10049093,10021140,10021133,10021130,10049093,10021132,10049093,10021140,10021133,10021130,10049093,10021132,10049093,10021140,10021133,10021130,10049093,10021132,10049093,10021140,10021134,10021130,10049093,10021132,10049093,10021140,10021134,10021130,10021127,10021132,10021127,10021140,10021134,10021130,10021127,10021135,10021127,10021140,10021137,10021130,10021127,10021135,10021127,10021140,10021137,10021130,10021127,10021135,10021127,10021140,10021138,10021130,10021127,10021135,10021127,10021140,10021138,10021130,10049094,10021135,10049094,10021145,10021139,10021130,10049094,10021136,10049094,10021145,10021139,10021130,10049094,10021136,10049094,10021145,10021142,10021130,10049094,10021136,10049094,10021145,10021142,10021130,10021128,10021136,10021128,10021145,10021143,10021130,10021128,10021136,10021128,10021145,10021143,10021130,10021128,10021136,10021128,10021145,10021147,10021130,10021128,10021144,10021128,10021145,10021147,10021130,10021128,10021144,10021128,10021145,10021147,10021130,10021129,10021144,10021129,10021146,10021130,10021129,10021144,10021129,10021146,10021130,10021129,10021144,10021129,10021146,10021130,10021129,10021144,10021129,10021146,10021130,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021146,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021131,10021141,10021141,10021141,10021141,10021141,10021141,10021141,10021141</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L27 W24/25; N=195; EHP=28521.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x24,normal:18x23,fast:30x6,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x10,swarm:84x54,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x10,heavy:127x3</t>
+          <t>L27 W24/25; N=195; EHP=79391.365849; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x6,fast:98x6,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x9,medium:123x10,normal:17x24,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10021151,10021162,10021153,10049095,10021161,10021154,10021169,10021151,10021162,10021153,10049095,10021161,10021154,10021151,10021162,10021153,10049095,10021161,10021155,10021151,10021162,10021153,10049095,10021161,10021155,10021151,10021162,10021153,10021148,10021161,10021155,10021151,10021162,10021153,10021148,10021161,10021158,10021151,10021162,10021156,10021148,10021161,10021158,10021151,10021162,10021156,10021148,10021161,10021158,10021151,10021162,10021156,10021148,10021161,10021159,10021151,10021162,10021156,10049096,10021161,10021159,10021151,10021162,10021156,10049096,10021166,10021159,10021151,10021162,10021156,10049096,10021166,10021160,10021151,10021162,10021157,10049096,10021166,10021160,10021151,10021162,10021157,10049096,10021166,10021163,10021151,10021162,10021157,10021149,10021166,10021163,10021151,10021162,10021157,10021149,10021166,10021164,10021151,10021162,10021157,10021149,10021166,10021164,10021151,10021162,10021157,10021149,10021166,10021168,10021151,10021162,10021165,10021149,10021166,10021168,10021151,10021162,10021165,10021150,10021166,10021168,10021151,10021162,10021165,10021150,10021167,10021151,10021162,10021165,10021150,10021167,10021151,10021162,10021165,10021150,10021167,10021152,10021162,10021165,10021150,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162</t>
+          <t>10021151,10049095,10021153,10049095,10021161,10021154,10021169,10021151,10049095,10021153,10049095,10021161,10021154,10021151,10049095,10021153,10049095,10021161,10021155,10021151,10049095,10021153,10049095,10021161,10021155,10021151,10021148,10021153,10021148,10021161,10021155,10021151,10021148,10021153,10021148,10021161,10021158,10021151,10021148,10021156,10021148,10021161,10021158,10021151,10021148,10021156,10021148,10021161,10021158,10021151,10021148,10021156,10021148,10021161,10021159,10021151,10049096,10021156,10049096,10021161,10021159,10021151,10049096,10021156,10049096,10021166,10021159,10021151,10049096,10021156,10049096,10021166,10021160,10021151,10049096,10021157,10049096,10021166,10021160,10021151,10049096,10021157,10049096,10021166,10021163,10021151,10021149,10021157,10021149,10021166,10021163,10021151,10021149,10021157,10021149,10021166,10021164,10021151,10021149,10021157,10021149,10021166,10021164,10021151,10021149,10021157,10021149,10021166,10021168,10021151,10021149,10021165,10021149,10021166,10021168,10021151,10021150,10021165,10021150,10021166,10021168,10021151,10021150,10021165,10021150,10021167,10021151,10021150,10021165,10021150,10021167,10021151,10021150,10021165,10021150,10021167,10021152,10021150,10021165,10021150,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021167,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021152,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162,10021162</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L27 W25/25; N=201; EHP=56921.000000; air:2x4,air:11x5,air:12x5,air:13x5,air:14x5,normal:17x23,normal:18x23,fast:30x6,heavy:31x2,heavy:40x3,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x56,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x10,heavy:127x3,boss:132x1</t>
+          <t>L27 W25/25; N=201; EHP=158432.046885; air:2x8,air:11x10,air:12x10,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x10,medium:123x10,normal:17x23,normal:18x23,swarm:84x32 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L27/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L27/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>228</v>
+        <v>370</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>221</v>
+        <v>330</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>214</v>
+        <v>290</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>207</v>
+        <v>380</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>193</v>
+        <v>380</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>186</v>
+        <v>310</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>172</v>
+        <v>320</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>158</v>
+        <v>320</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>151</v>
+        <v>380</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>144</v>
+        <v>310</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>137</v>
+        <v>290</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>130</v>
+        <v>215</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>380</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>320</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>380</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
